--- a/diseases/d169/2015-2019.xlsx
+++ b/diseases/d169/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1499,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1940,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.001961403059472987</v>
       </c>
@@ -2393,9 +2381,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.001961403059472987</v>
       </c>
@@ -2837,9 +2822,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.001961403059472987</v>
       </c>
@@ -3281,9 +3263,6 @@
       <c r="O19" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.005884209178418961</v>
       </c>
@@ -3725,9 +3704,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4169,9 +4145,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4613,9 +4586,6 @@
       <c r="O28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.007845612237891948</v>
       </c>
@@ -5057,9 +5027,6 @@
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.005884209178418961</v>
       </c>
@@ -5501,9 +5468,6 @@
       <c r="O34" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.003922806118945974</v>
       </c>
@@ -5945,9 +5909,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6389,9 +6350,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -6685,9 +6643,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -6981,9 +6936,6 @@
       <c r="O44" t="n">
         <v>3</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.00584819957035617</v>
       </c>
@@ -7277,9 +7229,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -7721,9 +7670,6 @@
       <c r="O49" t="n">
         <v>3</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.00584819957035617</v>
       </c>
@@ -8165,9 +8111,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -8609,9 +8552,6 @@
       <c r="O55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -9053,9 +8993,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -9349,9 +9286,6 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.00584819957035617</v>
       </c>
@@ -9645,9 +9579,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -10089,9 +10020,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -10533,9 +10461,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10754,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11195,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11717,9 +11636,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -12161,9 +12077,6 @@
       <c r="O79" t="n">
         <v>3</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.005826796097029401</v>
       </c>
@@ -12605,9 +12518,6 @@
       <c r="O82" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.005826796097029401</v>
       </c>
@@ -13049,9 +12959,6 @@
       <c r="O85" t="n">
         <v>2</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.003884530731352934</v>
       </c>
@@ -13493,9 +13400,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -13937,9 +13841,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14233,9 +14134,6 @@
       <c r="O93" t="n">
         <v>5</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.009711326828382336</v>
       </c>
@@ -14677,9 +14575,6 @@
       <c r="O96" t="n">
         <v>3</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.005826796097029401</v>
       </c>
@@ -14973,9 +14868,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15309,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -15861,9 +15750,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16305,9 +16191,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -16749,9 +16632,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -17045,9 +16925,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17489,9 +17366,6 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -17933,9 +17807,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18377,9 +18248,6 @@
       <c r="O121" t="n">
         <v>3</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.005809349466335731</v>
       </c>
@@ -18821,9 +18689,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -19265,9 +19130,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.00387289964422382</v>
       </c>
@@ -19709,9 +19571,6 @@
       <c r="O130" t="n">
         <v>3</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.005809349466335731</v>
       </c>
@@ -20005,9 +19864,6 @@
       <c r="O132" t="n">
         <v>5</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.00968224911055955</v>
       </c>
@@ -20301,9 +20157,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -20745,9 +20598,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -21041,9 +20891,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -21485,9 +21332,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -21929,9 +21773,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -22373,9 +22214,6 @@
       <c r="O148" t="n">
         <v>3</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.005795103006603752</v>
       </c>
@@ -22817,9 +22655,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -23261,9 +23096,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -23705,9 +23537,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -24149,9 +23978,6 @@
       <c r="O160" t="n">
         <v>3</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.005795103006603752</v>
       </c>
@@ -24593,9 +24419,6 @@
       <c r="O163" t="n">
         <v>4</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.007726804008805003</v>
       </c>
@@ -25036,9 +24859,6 @@
       </c>
       <c r="O166" t="n">
         <v>2</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0.003863402004402502</v>
